--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N88_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N88_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.54400374531753</v>
+        <v>1.388400608614099</v>
       </c>
       <c r="D2" t="n">
-        <v>9.332627234970362</v>
+        <v>1.516551925682684</v>
       </c>
       <c r="E2" t="n">
-        <v>9.798533642930837</v>
+        <v>1.592261716976261</v>
       </c>
       <c r="F2" t="n">
-        <v>11.37616471695901</v>
+        <v>1.848626766505839</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.1410710311792</v>
+        <v>4.57292404256662</v>
       </c>
       <c r="D3" t="n">
-        <v>32.08495666888837</v>
+        <v>5.213805458694361</v>
       </c>
       <c r="E3" t="n">
-        <v>9.798533642930837</v>
+        <v>1.592261716976261</v>
       </c>
       <c r="F3" t="n">
-        <v>11.37616471695901</v>
+        <v>1.848626766505839</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
